--- a/output/pdf_financials_xlsx/DDD.xlsx
+++ b/output/pdf_financials_xlsx/DDD.xlsx
@@ -3326,7 +3326,11 @@
           <t>Prepaids and deposits 7</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DDD.xlsx
+++ b/output/pdf_financials_xlsx/DDD.xlsx
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">

--- a/output/pdf_financials_xlsx/DDD.xlsx
+++ b/output/pdf_financials_xlsx/DDD.xlsx
@@ -562,10 +562,10 @@
         <v>0.005727</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.5198430000000001</v>
+        <v>0.567237</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.454023</v>
+        <v>0.97607</v>
       </c>
     </row>
     <row r="8">
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>4.620459</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.431037</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.171536</v>
       </c>
     </row>
     <row r="65">
@@ -1801,10 +1801,10 @@
         <v>0.037921</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.71312</v>
+        <v>1.144157</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1.560105</v>
+        <v>1.731641</v>
       </c>
     </row>
     <row r="69">
@@ -2610,13 +2610,13 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.108281</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.033694</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.11497</v>
       </c>
     </row>
     <row r="111">
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007662</v>
       </c>
     </row>
     <row r="112">
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007662</v>
       </c>
     </row>
     <row r="135">
@@ -3103,7 +3103,7 @@
         <v>-0.330631</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-7.793359</v>
+        <v>-7.801021</v>
       </c>
     </row>
   </sheetData>
@@ -5012,7 +5012,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -5510,7 +5514,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -5584,7 +5592,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -6482,7 +6494,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="n">
         <v>0.005</v>
       </c>
@@ -7376,7 +7392,11 @@
           <t>Management and directors' fees 14</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
